--- a/artfynd/A 4365-2022 artfynd.xlsx
+++ b/artfynd/A 4365-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4365-2022 artfynd.xlsx
+++ b/artfynd/A 4365-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>74543158</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>697755.9249891196</v>
+        <v>697756</v>
       </c>
       <c r="R2" t="n">
-        <v>7093817.101766688</v>
+        <v>7093817</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74543270</v>
+        <v>104166234</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kavelbroåsen, Ång</t>
+          <t>Kavelbroåsen, Balsjö, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>697930.1509788138</v>
+        <v>697811</v>
       </c>
       <c r="R3" t="n">
-        <v>7094246.846446398</v>
+        <v>7094078</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,31 +853,45 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74543269</v>
+        <v>74543179</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,39 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kavelbroåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>697835.8462762419</v>
+        <v>697747</v>
       </c>
       <c r="R4" t="n">
-        <v>7094075.864814039</v>
+        <v>7093811</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +956,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,19 +985,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74543179</v>
+        <v>74543180</v>
       </c>
       <c r="B5" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1046,12 +1005,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>697747.0457652819</v>
+        <v>697782</v>
       </c>
       <c r="R5" t="n">
-        <v>7093810.803446135</v>
+        <v>7093923</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1094,19 +1053,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74543180</v>
+        <v>104166233</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,37 +1093,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kavelbroåsen, Ång</t>
+          <t>Kavelbroåsen, Balsjö, Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>697781.9198475594</v>
+        <v>697805</v>
       </c>
       <c r="R6" t="n">
-        <v>7093922.878053115</v>
+        <v>7094076</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,35 +1163,49 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>74543267</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1290,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>697742.8174326988</v>
+        <v>697743</v>
       </c>
       <c r="R7" t="n">
-        <v>7093800.82848464</v>
+        <v>7093801</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,19 +1271,9 @@
           <t>2018-10-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,53 +1300,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104166234</v>
+        <v>74543268</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kavelbroåsen, Balsjö, Bjurholm, Ång</t>
+          <t>Kavelbroåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>697810.9829933582</v>
+        <v>697746</v>
       </c>
       <c r="R8" t="n">
-        <v>7094077.819310786</v>
+        <v>7093842</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,22 +1370,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,88 +1386,69 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anna Hallmén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104166233</v>
+        <v>74543269</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kavelbroåsen, Balsjö, Bjurholm, Ång</t>
+          <t>Kavelbroåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>697804.9341971396</v>
+        <v>697836</v>
       </c>
       <c r="R9" t="n">
-        <v>7094075.671339186</v>
+        <v>7094076</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,22 +1472,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,38 +1488,121 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anna Hallmén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74543270</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kavelbroåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>697930</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7094247</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4365-2022 artfynd.xlsx
+++ b/artfynd/A 4365-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543158</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104166234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543179</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543180</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104166233</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543267</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543268</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543269</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,8 +1648,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74543270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>